--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
@@ -70,19 +73,16 @@
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>Rigetti Computing, Inc.</t>
-  </si>
-  <si>
     <t>International Business Machines</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>QBTS</t>
   </si>
   <si>
     <t>IONQ</t>
-  </si>
-  <si>
-    <t>RGTI</t>
   </si>
   <si>
     <t>IBM</t>
@@ -516,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>27.75</v>
       </c>
       <c r="E2">
-        <v>59.2</v>
+        <v>55.4</v>
       </c>
       <c r="F2">
-        <v>19.1</v>
+        <v>16.21</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,37 +563,37 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>52.69</v>
+        <v>27.83</v>
       </c>
       <c r="E3">
-        <v>58.9</v>
+        <v>62.5</v>
       </c>
       <c r="F3">
-        <v>6.88</v>
+        <v>23.69</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>57.7</v>
+        <v>60.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>28.11</v>
+        <v>54.1</v>
       </c>
       <c r="E4">
-        <v>56.5</v>
+        <v>58</v>
       </c>
       <c r="F4">
-        <v>9.93</v>
+        <v>15.28</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I4">
         <v>66</v>
       </c>
       <c r="J4">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -657,28 +657,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>307.94</v>
+        <v>310.93</v>
       </c>
       <c r="E5">
-        <v>52.1</v>
+        <v>76.2</v>
       </c>
       <c r="F5">
-        <v>-0.21</v>
+        <v>3.03</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I5">
         <v>66</v>
       </c>
       <c r="J5">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K5">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -516,13 +516,13 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>27.75</v>
+        <v>28.22</v>
       </c>
       <c r="E2">
-        <v>55.4</v>
+        <v>56.8</v>
       </c>
       <c r="F2">
-        <v>16.21</v>
+        <v>18.17</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -537,7 +537,7 @@
         <v>80</v>
       </c>
       <c r="K2">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,13 +563,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>27.83</v>
+        <v>28.33</v>
       </c>
       <c r="E3">
-        <v>62.5</v>
+        <v>64.2</v>
       </c>
       <c r="F3">
-        <v>23.69</v>
+        <v>25.91</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -581,19 +581,19 @@
         <v>70</v>
       </c>
       <c r="J3">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,13 +610,13 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>54.1</v>
+        <v>54.44</v>
       </c>
       <c r="E4">
-        <v>58</v>
+        <v>58.6</v>
       </c>
       <c r="F4">
-        <v>15.28</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>60</v>
@@ -631,7 +631,7 @@
         <v>66</v>
       </c>
       <c r="K4">
-        <v>58.8</v>
+        <v>58.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -657,13 +657,13 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>310.93</v>
+        <v>310.48</v>
       </c>
       <c r="E5">
-        <v>76.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F5">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -678,7 +678,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>55.8</v>
+        <v>55.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum Inc.</t>
+  </si>
+  <si>
+    <t>International Business Machines</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>D-Wave Quantum Inc.</t>
-  </si>
-  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>International Business Machines</t>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>IBM</t>
   </si>
   <si>
     <t>RGTI</t>
   </si>
   <si>
-    <t>QBTS</t>
-  </si>
-  <si>
     <t>IONQ</t>
-  </si>
-  <si>
-    <t>IBM</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -516,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>28.22</v>
+        <v>26.1</v>
       </c>
       <c r="E2">
-        <v>56.8</v>
+        <v>64.2</v>
       </c>
       <c r="F2">
-        <v>18.17</v>
+        <v>-3.33</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J2">
         <v>80</v>
       </c>
       <c r="K2">
-        <v>61.1</v>
+        <v>63.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,28 +563,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28.33</v>
+        <v>309.24</v>
       </c>
       <c r="E3">
-        <v>64.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F3">
-        <v>25.91</v>
+        <v>0.42</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
+        <v>73</v>
+      </c>
+      <c r="I3">
+        <v>66</v>
+      </c>
+      <c r="J3">
         <v>60</v>
       </c>
-      <c r="I3">
-        <v>70</v>
-      </c>
-      <c r="J3">
-        <v>76</v>
-      </c>
       <c r="K3">
-        <v>59.9</v>
+        <v>58.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>54.44</v>
+        <v>25.84</v>
       </c>
       <c r="E4">
-        <v>58.6</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>-8.08</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K4">
-        <v>58.3</v>
+        <v>55.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -657,28 +657,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>310.48</v>
+        <v>50.35</v>
       </c>
       <c r="E5">
-        <v>75.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5">
-        <v>2.88</v>
+        <v>-4.44</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>55.3</v>
+        <v>53.2</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,37 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>IonQ, Inc.</t>
+  </si>
+  <si>
     <t>International Business Machines</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>IonQ, Inc.</t>
-  </si>
-  <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>IONQ</t>
+  </si>
+  <si>
     <t>IBM</t>
   </si>
   <si>
     <t>RGTI</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>26.1</v>
+        <v>25.29</v>
       </c>
       <c r="E2">
-        <v>64.2</v>
+        <v>46.9</v>
       </c>
       <c r="F2">
-        <v>-3.33</v>
+        <v>1.61</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>63.6</v>
+        <v>54.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,40 +560,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>309.24</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>66.90000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="F3">
-        <v>0.42</v>
+        <v>-0.95</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="I3">
+        <v>63</v>
+      </c>
+      <c r="J3">
         <v>66</v>
       </c>
-      <c r="J3">
-        <v>60</v>
-      </c>
       <c r="K3">
-        <v>58.6</v>
+        <v>49.8</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>51.940834218365</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
-      </c>
-      <c r="N3">
-        <v>47.37006702605126</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,40 +607,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>25.84</v>
+        <v>305.09</v>
       </c>
       <c r="E4">
-        <v>56</v>
+        <v>43.5</v>
       </c>
       <c r="F4">
-        <v>-8.08</v>
+        <v>1.54</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>55.4</v>
+        <v>48.6</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
+        <v>51.940834218365</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
-      </c>
-      <c r="N4">
-        <v>47.37006702605126</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,40 +654,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>50.35</v>
+        <v>22.38</v>
       </c>
       <c r="E5">
-        <v>65.59999999999999</v>
+        <v>33.4</v>
       </c>
       <c r="F5">
-        <v>-4.44</v>
+        <v>-1.93</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>53.2</v>
+        <v>42.8</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>51.940834218365</v>
+      </c>
+      <c r="O5" t="s">
         <v>26</v>
-      </c>
-      <c r="N5">
-        <v>47.37006702605126</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>Rigetti Computing, Inc.</t>
+  </si>
+  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
     <t>International Business Machines</t>
   </si>
   <si>
-    <t>Rigetti Computing, Inc.</t>
-  </si>
-  <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>IONQ</t>
   </si>
   <si>
     <t>IBM</t>
-  </si>
-  <si>
-    <t>RGTI</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>25.29</v>
+        <v>28.13</v>
       </c>
       <c r="E2">
-        <v>46.9</v>
+        <v>50.3</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>54.6</v>
+        <v>55.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>23.6</v>
       </c>
       <c r="E3">
-        <v>40.5</v>
+        <v>39.8</v>
       </c>
       <c r="F3">
-        <v>-0.95</v>
+        <v>-3.71</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>49.8</v>
+        <v>44.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>305.09</v>
+        <v>46.77</v>
       </c>
       <c r="E4">
-        <v>43.5</v>
+        <v>41.2</v>
       </c>
       <c r="F4">
-        <v>1.54</v>
+        <v>-6.12</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>63</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>48.6</v>
+        <v>43.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>22.38</v>
+        <v>291.5</v>
       </c>
       <c r="E5">
-        <v>33.4</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>-1.93</v>
+        <v>-4.29</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>42.8</v>
+        <v>34.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>IonQ, Inc.</t>
+  </si>
+  <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>IonQ, Inc.</t>
-  </si>
-  <si>
     <t>International Business Machines</t>
   </si>
   <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>IONQ</t>
+  </si>
+  <si>
     <t>RGTI</t>
-  </si>
-  <si>
-    <t>IONQ</t>
   </si>
   <si>
     <t>IBM</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>28.13</v>
+        <v>31.27</v>
       </c>
       <c r="E2">
-        <v>50.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>19.58</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>63</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>55.5</v>
+        <v>56.7</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>23.6</v>
+        <v>50.76</v>
       </c>
       <c r="E3">
-        <v>39.8</v>
+        <v>57.7</v>
       </c>
       <c r="F3">
-        <v>-3.71</v>
+        <v>12.18</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H3">
+        <v>56</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="I3">
-        <v>66</v>
-      </c>
       <c r="J3">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>44.9</v>
+        <v>52.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>46.77</v>
+        <v>25.38</v>
       </c>
       <c r="E4">
-        <v>41.2</v>
+        <v>56.3</v>
       </c>
       <c r="F4">
-        <v>-6.12</v>
+        <v>13.96</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>43.7</v>
+        <v>50.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>291.5</v>
+        <v>302.47</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>42.1</v>
       </c>
       <c r="F5">
-        <v>-4.29</v>
+        <v>-1.07</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>60</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>34.9</v>
+        <v>37.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -534,7 +534,7 @@
         <v>76</v>
       </c>
       <c r="K2">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -581,7 +581,7 @@
         <v>63</v>
       </c>
       <c r="K3">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -628,7 +628,7 @@
         <v>80</v>
       </c>
       <c r="K4">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>60</v>
       </c>
       <c r="K5">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>Rigetti Computing, Inc.</t>
+  </si>
+  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>Rigetti Computing, Inc.</t>
-  </si>
-  <si>
     <t>International Business Machines</t>
   </si>
   <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>IONQ</t>
-  </si>
-  <si>
-    <t>RGTI</t>
   </si>
   <si>
     <t>IBM</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>31.27</v>
+        <v>30.2</v>
       </c>
       <c r="E2">
-        <v>65.09999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="F2">
-        <v>19.58</v>
+        <v>15.05</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K2">
-        <v>56.8</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>50.76</v>
+        <v>25.21</v>
       </c>
       <c r="E3">
-        <v>57.7</v>
+        <v>54.4</v>
       </c>
       <c r="F3">
-        <v>12.18</v>
+        <v>12.49</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>25.38</v>
+        <v>49.78</v>
       </c>
       <c r="E4">
-        <v>56.3</v>
+        <v>50.2</v>
       </c>
       <c r="F4">
-        <v>13.96</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>51</v>
+        <v>52.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>302.47</v>
+        <v>296.73</v>
       </c>
       <c r="E5">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="F5">
-        <v>-1.07</v>
+        <v>-1.76</v>
       </c>
       <c r="G5">
         <v>20</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I5">
         <v>46</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>날짜</t>
   </si>
@@ -61,27 +61,27 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
-    <t>Rigetti Computing, Inc.</t>
-  </si>
-  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
     <t>International Business Machines</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>QBTS</t>
   </si>
   <si>
-    <t>RGTI</t>
-  </si>
-  <si>
     <t>IONQ</t>
   </si>
   <si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -513,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>30.2</v>
+        <v>24.72</v>
       </c>
       <c r="E2">
-        <v>59.6</v>
+        <v>57.3</v>
       </c>
       <c r="F2">
-        <v>15.05</v>
+        <v>4.75</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>59.1</v>
+        <v>63.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,10 +546,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -560,40 +563,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>25.21</v>
+        <v>28.11</v>
       </c>
       <c r="E3">
-        <v>54.4</v>
+        <v>56.8</v>
       </c>
       <c r="F3">
-        <v>12.49</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>54.5</v>
+        <v>59.3</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -607,40 +610,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>49.78</v>
+        <v>49.45</v>
       </c>
       <c r="E4">
-        <v>50.2</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>9.869999999999999</v>
+        <v>5.73</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K4">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -654,40 +657,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>296.73</v>
+        <v>304.22</v>
       </c>
       <c r="E5">
-        <v>41.8</v>
+        <v>54.3</v>
       </c>
       <c r="F5">
-        <v>-1.76</v>
+        <v>4.36</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>37.5</v>
+        <v>51.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -537,7 +537,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -584,7 +584,7 @@
         <v>73</v>
       </c>
       <c r="K3">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -631,7 +631,7 @@
         <v>70</v>
       </c>
       <c r="K4">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -678,7 +678,7 @@
         <v>60</v>
       </c>
       <c r="K5">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
@@ -70,28 +70,25 @@
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>International Business Machines</t>
+  </si>
+  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>International Business Machines</t>
-  </si>
-  <si>
     <t>RGTI</t>
   </si>
   <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>IBM</t>
+  </si>
+  <si>
     <t>IONQ</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>24.72</v>
+        <v>25.53</v>
       </c>
       <c r="E2">
-        <v>57.3</v>
+        <v>56.9</v>
       </c>
       <c r="F2">
-        <v>4.75</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="J2">
         <v>83</v>
       </c>
       <c r="K2">
-        <v>63.6</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,13 +560,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28.11</v>
+        <v>28.8</v>
       </c>
       <c r="E3">
-        <v>56.8</v>
+        <v>54.4</v>
       </c>
       <c r="F3">
-        <v>-0.07000000000000001</v>
+        <v>-6.01</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -581,22 +578,22 @@
         <v>73</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>59.4</v>
+        <v>58.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
-      </c>
-      <c r="N3">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,40 +607,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>49.45</v>
+        <v>312.18</v>
       </c>
       <c r="E4">
-        <v>56</v>
+        <v>60.9</v>
       </c>
       <c r="F4">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
+        <v>56</v>
+      </c>
+      <c r="I4">
         <v>60</v>
       </c>
-      <c r="I4">
-        <v>46</v>
-      </c>
       <c r="J4">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>51.6</v>
+        <v>56.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
-      </c>
-      <c r="N4">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,40 +654,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>304.22</v>
+        <v>50.95</v>
       </c>
       <c r="E5">
-        <v>54.3</v>
+        <v>55</v>
       </c>
       <c r="F5">
-        <v>4.36</v>
+        <v>4.6</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H5">
         <v>60</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>51.2</v>
+        <v>54.8</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O5" t="s">
         <v>26</v>
-      </c>
-      <c r="N5">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum Inc.</t>
+  </si>
+  <si>
+    <t>International Business Machines</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>D-Wave Quantum Inc.</t>
-  </si>
-  <si>
-    <t>International Business Machines</t>
-  </si>
-  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
     <t>RGTI</t>
-  </si>
-  <si>
-    <t>QBTS</t>
-  </si>
-  <si>
-    <t>IBM</t>
   </si>
   <si>
     <t>IONQ</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>25.53</v>
+        <v>28.82</v>
       </c>
       <c r="E2">
-        <v>56.9</v>
+        <v>40.1</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>-7.83</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J2">
         <v>83</v>
       </c>
       <c r="K2">
-        <v>58.8</v>
+        <v>59.9</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28.8</v>
+        <v>303.16</v>
       </c>
       <c r="E3">
-        <v>54.4</v>
+        <v>50.3</v>
       </c>
       <c r="F3">
-        <v>-6.01</v>
+        <v>0.23</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>63</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>58.6</v>
+        <v>56.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>312.18</v>
+        <v>24.47</v>
       </c>
       <c r="E4">
-        <v>60.9</v>
+        <v>38.9</v>
       </c>
       <c r="F4">
-        <v>5.83</v>
+        <v>-3.59</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>56.4</v>
+        <v>51.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>50.95</v>
+        <v>48.94</v>
       </c>
       <c r="E5">
-        <v>55</v>
+        <v>38.4</v>
       </c>
       <c r="F5">
-        <v>4.6</v>
+        <v>-3.59</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>54.8</v>
+        <v>44.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
@@ -70,19 +73,16 @@
     <t>International Business Machines</t>
   </si>
   <si>
-    <t>Rigetti Computing, Inc.</t>
-  </si>
-  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>QBTS</t>
   </si>
   <si>
     <t>IBM</t>
-  </si>
-  <si>
-    <t>RGTI</t>
   </si>
   <si>
     <t>IONQ</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>28.82</v>
+        <v>25.62</v>
       </c>
       <c r="E2">
-        <v>40.1</v>
+        <v>67</v>
       </c>
       <c r="F2">
-        <v>-7.83</v>
+        <v>3.64</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
+        <v>60</v>
+      </c>
+      <c r="I2">
+        <v>63</v>
+      </c>
+      <c r="J2">
         <v>80</v>
       </c>
-      <c r="I2">
-        <v>80</v>
-      </c>
-      <c r="J2">
-        <v>83</v>
-      </c>
       <c r="K2">
-        <v>59.9</v>
+        <v>55.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>303.16</v>
+        <v>28.83</v>
       </c>
       <c r="E3">
-        <v>50.3</v>
+        <v>63.7</v>
       </c>
       <c r="F3">
-        <v>0.23</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>56.1</v>
+        <v>55.3</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>24.47</v>
+        <v>305.67</v>
       </c>
       <c r="E4">
-        <v>38.9</v>
+        <v>50.4</v>
       </c>
       <c r="F4">
-        <v>-3.59</v>
+        <v>0.48</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
+        <v>53</v>
+      </c>
+      <c r="I4">
         <v>63</v>
       </c>
-      <c r="I4">
-        <v>66</v>
-      </c>
       <c r="J4">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>51.3</v>
+        <v>55.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>48.94</v>
+        <v>50.8</v>
       </c>
       <c r="E5">
-        <v>38.4</v>
+        <v>61</v>
       </c>
       <c r="F5">
-        <v>-3.59</v>
+        <v>2.73</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K5">
-        <v>44.9</v>
+        <v>54.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,40 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>IonQ, Inc.</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>D-Wave Quantum Inc.</t>
-  </si>
-  <si>
     <t>International Business Machines</t>
   </si>
   <si>
-    <t>IonQ, Inc.</t>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>QBTS</t>
   </si>
   <si>
     <t>RGTI</t>
   </si>
   <si>
-    <t>QBTS</t>
-  </si>
-  <si>
     <t>IBM</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>25.62</v>
+        <v>38.34</v>
       </c>
       <c r="E2">
-        <v>67</v>
+        <v>56.1</v>
       </c>
       <c r="F2">
-        <v>3.64</v>
+        <v>24.56</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
         <v>60</v>
       </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
       <c r="J2">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>55.3</v>
+        <v>48.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28.83</v>
+        <v>18.94</v>
       </c>
       <c r="E3">
-        <v>63.7</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>4.93</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I3">
+        <v>76</v>
+      </c>
+      <c r="J3">
         <v>63</v>
       </c>
-      <c r="J3">
-        <v>83</v>
-      </c>
       <c r="K3">
-        <v>55.3</v>
+        <v>45.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>305.67</v>
+        <v>17.69</v>
       </c>
       <c r="E4">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F4">
-        <v>0.48</v>
+        <v>10.42</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
+        <v>50</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
         <v>53</v>
       </c>
-      <c r="I4">
-        <v>63</v>
-      </c>
-      <c r="J4">
-        <v>50</v>
-      </c>
       <c r="K4">
-        <v>55.3</v>
+        <v>44.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,16 +654,16 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>50.8</v>
+        <v>239.37</v>
       </c>
       <c r="E5">
-        <v>61</v>
+        <v>23.7</v>
       </c>
       <c r="F5">
-        <v>2.73</v>
+        <v>7.17</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>56</v>
@@ -672,10 +672,10 @@
         <v>60</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>54.1</v>
+        <v>36.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>IonQ, Inc.</t>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -513,19 +516,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>38.34</v>
+        <v>35.73</v>
       </c>
       <c r="E2">
-        <v>56.1</v>
+        <v>54.2</v>
       </c>
       <c r="F2">
-        <v>24.56</v>
+        <v>-6.88</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I2">
         <v>60</v>
@@ -534,7 +537,7 @@
         <v>53</v>
       </c>
       <c r="K2">
-        <v>48.1</v>
+        <v>40.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,10 +546,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -560,40 +563,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>18.94</v>
+        <v>18.59</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>43.9</v>
       </c>
       <c r="F3">
-        <v>4.93</v>
+        <v>-1.01</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
+        <v>50</v>
+      </c>
+      <c r="I3">
+        <v>73</v>
+      </c>
+      <c r="J3">
         <v>70</v>
       </c>
-      <c r="I3">
-        <v>76</v>
-      </c>
-      <c r="J3">
-        <v>63</v>
-      </c>
       <c r="K3">
-        <v>45.5</v>
+        <v>39.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -607,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>17.69</v>
+        <v>17.01</v>
       </c>
       <c r="E4">
-        <v>50.5</v>
+        <v>55.3</v>
       </c>
       <c r="F4">
-        <v>10.42</v>
+        <v>-2.35</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>50</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>44.1</v>
+        <v>38.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,10 +640,10 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -654,28 +657,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>239.37</v>
+        <v>258.85</v>
       </c>
       <c r="E5">
-        <v>23.7</v>
+        <v>48</v>
       </c>
       <c r="F5">
-        <v>7.17</v>
+        <v>7.76</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J5">
         <v>56</v>
       </c>
       <c r="K5">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,10 +687,10 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -537,7 +537,7 @@
         <v>53</v>
       </c>
       <c r="K2">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -584,7 +584,7 @@
         <v>70</v>
       </c>
       <c r="K3">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -631,7 +631,7 @@
         <v>60</v>
       </c>
       <c r="K4">
-        <v>38.7</v>
+        <v>37.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -678,7 +678,7 @@
         <v>56</v>
       </c>
       <c r="K5">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,43 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>D-Wave Quantum Inc.</t>
+    <t>International Business Machines</t>
   </si>
   <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>International Business Machines</t>
+    <t>QBTS</t>
   </si>
   <si>
     <t>IONQ</t>
   </si>
   <si>
-    <t>QBTS</t>
+    <t>IBM</t>
   </si>
   <si>
     <t>RGTI</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>35.73</v>
+        <v>19.04</v>
       </c>
       <c r="E2">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="F2">
-        <v>-6.88</v>
+        <v>0.53</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>39</v>
+        <v>54.9</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,40 +560,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>18.59</v>
+        <v>35.87</v>
       </c>
       <c r="E3">
-        <v>43.9</v>
+        <v>57.3</v>
       </c>
       <c r="F3">
-        <v>-1.01</v>
+        <v>-6.44</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>38.2</v>
+        <v>51.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>32.23518188264562</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>17.01</v>
+        <v>253.33</v>
       </c>
       <c r="E4">
-        <v>55.3</v>
+        <v>47.2</v>
       </c>
       <c r="F4">
-        <v>-2.35</v>
+        <v>5.83</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>56</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>37.4</v>
+        <v>44.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,10 +637,10 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,13 +654,13 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>258.85</v>
+        <v>17.6</v>
       </c>
       <c r="E5">
-        <v>48</v>
+        <v>61.4</v>
       </c>
       <c r="F5">
-        <v>7.76</v>
+        <v>-0.51</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -672,13 +669,13 @@
         <v>60</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <v>56</v>
       </c>
       <c r="K5">
-        <v>36.2</v>
+        <v>43.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,10 +684,10 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>날짜</t>
   </si>
@@ -61,40 +61,43 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>International Business Machines</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>Rigetti Computing, Inc.</t>
+  </si>
+  <si>
     <t>IonQ, Inc.</t>
   </si>
   <si>
-    <t>International Business Machines</t>
-  </si>
-  <si>
-    <t>Rigetti Computing, Inc.</t>
+    <t>IBM</t>
   </si>
   <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>RGTI</t>
+  </si>
+  <si>
     <t>IONQ</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>RGTI</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -513,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>19.04</v>
+        <v>250.2</v>
       </c>
       <c r="E2">
-        <v>53.7</v>
+        <v>44</v>
       </c>
       <c r="F2">
-        <v>0.53</v>
+        <v>2.01</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>54.9</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,10 +546,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -560,40 +563,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>35.87</v>
+        <v>18.76</v>
       </c>
       <c r="E3">
-        <v>57.3</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>-6.44</v>
+        <v>2.85</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>51.1</v>
+        <v>54.2</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -607,40 +610,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>253.33</v>
+        <v>16.99</v>
       </c>
       <c r="E4">
-        <v>47.2</v>
+        <v>54.6</v>
       </c>
       <c r="F4">
-        <v>5.83</v>
+        <v>0.18</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>44.1</v>
+        <v>51</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -654,40 +657,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>17.6</v>
+        <v>35.12</v>
       </c>
       <c r="E5">
-        <v>61.4</v>
+        <v>54.7</v>
       </c>
       <c r="F5">
-        <v>-0.51</v>
+        <v>-5.21</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>43.1</v>
+        <v>50.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>International Business Machines</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>250.2</v>
+        <v>248.87</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>45.7</v>
       </c>
       <c r="F2">
-        <v>2.01</v>
+        <v>-0.48</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I2">
         <v>80</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>56.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,40 +560,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>18.76</v>
+        <v>18.91</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>46.9</v>
       </c>
       <c r="F3">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>54.2</v>
+        <v>49.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
-      </c>
-      <c r="N3">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,40 +607,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>16.99</v>
+        <v>16.94</v>
       </c>
       <c r="E4">
-        <v>54.6</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>0.18</v>
+        <v>-4.62</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I4">
+        <v>46</v>
+      </c>
+      <c r="J4">
         <v>50</v>
       </c>
-      <c r="J4">
-        <v>60</v>
-      </c>
       <c r="K4">
-        <v>51</v>
+        <v>45.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
-      </c>
-      <c r="N4">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,40 +654,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>35.12</v>
+        <v>34.27</v>
       </c>
       <c r="E5">
-        <v>54.7</v>
+        <v>52.1</v>
       </c>
       <c r="F5">
-        <v>-5.21</v>
+        <v>-7.7</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>63</v>
       </c>
       <c r="I5">
+        <v>50</v>
+      </c>
+      <c r="J5">
         <v>56</v>
       </c>
-      <c r="J5">
-        <v>53</v>
-      </c>
       <c r="K5">
-        <v>50.4</v>
+        <v>44.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O5" t="s">
         <v>26</v>
-      </c>
-      <c r="N5">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
   </si>
   <si>
     <t>International Business Machines</t>
@@ -70,31 +70,31 @@
     <t>D-Wave Quantum Inc.</t>
   </si>
   <si>
+    <t>IonQ, Inc.</t>
+  </si>
+  <si>
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>IonQ, Inc.</t>
-  </si>
-  <si>
     <t>IBM</t>
   </si>
   <si>
     <t>QBTS</t>
   </si>
   <si>
+    <t>IONQ</t>
+  </si>
+  <si>
     <t>RGTI</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>248.87</v>
+        <v>245.07</v>
       </c>
       <c r="E2">
-        <v>45.7</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>-0.48</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>56.5</v>
+        <v>51.4</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>18.91</v>
+        <v>13.74</v>
       </c>
       <c r="E3">
-        <v>46.9</v>
+        <v>30.5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>49.5</v>
+        <v>48.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>16.94</v>
+        <v>28.49</v>
       </c>
       <c r="E4">
-        <v>52</v>
+        <v>35.1</v>
       </c>
       <c r="F4">
-        <v>-4.62</v>
+        <v>7.15</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>45.9</v>
+        <v>47.2</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>34.27</v>
+        <v>13.84</v>
       </c>
       <c r="E5">
-        <v>52.1</v>
+        <v>35.2</v>
       </c>
       <c r="F5">
-        <v>-7.7</v>
+        <v>7.29</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>44.5</v>
+        <v>43.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,40 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>D-Wave Quantum Inc.</t>
+  </si>
+  <si>
+    <t>Rigetti Computing, Inc.</t>
+  </si>
+  <si>
+    <t>IonQ, Inc.</t>
   </si>
   <si>
     <t>International Business Machines</t>
   </si>
   <si>
-    <t>D-Wave Quantum Inc.</t>
-  </si>
-  <si>
-    <t>IonQ, Inc.</t>
-  </si>
-  <si>
-    <t>Rigetti Computing, Inc.</t>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>RGTI</t>
+  </si>
+  <si>
+    <t>IONQ</t>
   </si>
   <si>
     <t>IBM</t>
   </si>
   <si>
-    <t>QBTS</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>RGTI</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>245.07</v>
+        <v>23.83</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>59.7</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>30.43</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>51.4</v>
+        <v>55.7</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>13.74</v>
+        <v>20.09</v>
       </c>
       <c r="E3">
-        <v>30.5</v>
+        <v>53.6</v>
       </c>
       <c r="F3">
-        <v>5.86</v>
+        <v>24.94</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>63</v>
+      </c>
+      <c r="I3">
+        <v>43</v>
+      </c>
+      <c r="J3">
         <v>53</v>
       </c>
-      <c r="I3">
-        <v>56</v>
-      </c>
-      <c r="J3">
-        <v>63</v>
-      </c>
       <c r="K3">
-        <v>48.4</v>
+        <v>52.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>28.49</v>
+        <v>52.57</v>
       </c>
       <c r="E4">
-        <v>35.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F4">
-        <v>7.15</v>
+        <v>24.84</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>53</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="K4">
-        <v>47.2</v>
+        <v>47.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>13.84</v>
+        <v>225.74</v>
       </c>
       <c r="E5">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F5">
-        <v>7.29</v>
+        <v>-0.6</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H5">
+        <v>43</v>
+      </c>
+      <c r="I5">
         <v>46</v>
       </c>
-      <c r="I5">
-        <v>36</v>
-      </c>
       <c r="J5">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>43.4</v>
+        <v>39.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/미장_양자_분석.xlsx
+++ b/DECISION/미장_양자_분석.xlsx
@@ -61,7 +61,13 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>International Business Machines</t>
+  </si>
+  <si>
+    <t>IonQ, Inc.</t>
   </si>
   <si>
     <t>D-Wave Quantum Inc.</t>
@@ -70,10 +76,10 @@
     <t>Rigetti Computing, Inc.</t>
   </si>
   <si>
-    <t>IonQ, Inc.</t>
-  </si>
-  <si>
-    <t>International Business Machines</t>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>IONQ</t>
   </si>
   <si>
     <t>QBTS</t>
@@ -82,19 +88,13 @@
     <t>RGTI</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>23.83</v>
+        <v>284.84</v>
       </c>
       <c r="E2">
-        <v>59.7</v>
+        <v>70.3</v>
       </c>
       <c r="F2">
-        <v>30.43</v>
+        <v>-4.35</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>55.7</v>
+        <v>41.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>20.09</v>
+        <v>56.78</v>
       </c>
       <c r="E3">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="F3">
-        <v>24.94</v>
+        <v>-21.22</v>
       </c>
       <c r="G3">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>63</v>
+      </c>
+      <c r="J3">
         <v>60</v>
       </c>
-      <c r="H3">
-        <v>63</v>
-      </c>
-      <c r="I3">
-        <v>43</v>
-      </c>
-      <c r="J3">
-        <v>53</v>
-      </c>
       <c r="K3">
-        <v>52.9</v>
+        <v>38.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>52.57</v>
+        <v>23.85</v>
       </c>
       <c r="E4">
-        <v>65.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="F4">
-        <v>24.84</v>
+        <v>-20.87</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H4">
+        <v>43</v>
+      </c>
+      <c r="I4">
         <v>53</v>
       </c>
-      <c r="I4">
-        <v>30</v>
-      </c>
       <c r="J4">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>47.7</v>
+        <v>34.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>225.74</v>
+        <v>20.68</v>
       </c>
       <c r="E5">
-        <v>27.7</v>
+        <v>55.5</v>
       </c>
       <c r="F5">
-        <v>-0.6</v>
+        <v>-19.03</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K5">
-        <v>39.1</v>
+        <v>32.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>
